--- a/docs/excel/仕様書.xlsx
+++ b/docs/excel/仕様書.xlsx
@@ -35,7 +35,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.1（リリース前の下書き）</t>
+    <t>0.2（リリース前の下書き。迷惑番号の確認を、登録フォームに統合）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -53,7 +53,7 @@
     <t>根拠</t>
   </si>
   <si>
-    <t>ソースコード（コミット 8a943ce 時点）。コードを読んで書いた。本番の AWS の実物は確認できていない</t>
+    <t>ソースコード（2026-10-19 時点）。コードを読んで書いた。本番の AWS の実物は確認できていない</t>
   </si>
   <si>
     <t>「未確認」と書いた箇所は、前任者や AWS の画面で確認するまで、推測を含む。</t>
@@ -65,7 +65,7 @@
     <t>社内で受けた電話の対応を支える Web システム。</t>
   </si>
   <si>
-    <t>・電話番号が、すでに「迷惑番号」として登録されているかを確認する（迷惑電話チェック）</t>
+    <t>・電話番号を入力すると、すでに「迷惑番号」として登録されているかを、自動で確認する（登録フォームの中で）</t>
   </si>
   <si>
     <t>・迷惑でなければ、電話の伝言を登録し、Teams のチャネルへメールで通知する</t>
@@ -86,22 +86,22 @@
     <t>電話を受ける</t>
   </si>
   <si>
-    <t xml:space="preserve">  └ 迷惑電話チェック（番号を入力して検索）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       ├ 迷惑番号に登録されている → 着信を記録する（対応者・メモ）</t>
+    <t xml:space="preserve">  └ 登録フォームの「電話番号」に入力（自動で、迷惑番号か確認）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       ├ 迷惑番号に登録されている → 赤い札とカード。着信を記録する（対応者・メモ）</t>
   </si>
   <si>
     <t xml:space="preserve">       └ 登録なし</t>
   </si>
   <si>
-    <t xml:space="preserve">            ├ 通常の電話 → 「伝言を登録する」→ 登録フォーム → 確認 → 登録 → Teams に通知</t>
+    <t xml:space="preserve">            ├ 通常の電話 → そのまま伝言を入力 → 確認 → 登録 → Teams に通知</t>
   </si>
   <si>
     <t xml:space="preserve">            └ 迷惑電話だった → 「迷惑番号として登録する」→ 迷惑番号一覧の登録フォーム</t>
   </si>
   <si>
-    <t>画面上部の矢印のタブは、この順（迷惑電話チェック → 登録フォーム → 伝言一覧）に並ぶ。</t>
+    <t>画面上部の矢印のタブは、この順（登録フォーム → 伝言一覧 → 迷惑番号一覧）に並ぶ。</t>
   </si>
   <si>
     <t>3. 環境</t>
@@ -182,22 +182,13 @@
     <t>/</t>
   </si>
   <si>
-    <t>/nuisance へ移動する</t>
-  </si>
-  <si>
-    <t>迷惑電話チェック</t>
-  </si>
-  <si>
-    <t>/nuisance</t>
-  </si>
-  <si>
-    <t>電話番号を入力して検索。結果は2種類（下記）。右上の「迷惑番号一覧」へ</t>
+    <t>/register へ移動する</t>
   </si>
   <si>
     <t>迷惑番号一覧</t>
   </si>
   <si>
-    <t>/nuisance/list</t>
+    <t>/nuisance/list（/nuisance は、登録フォームへ移動）</t>
   </si>
   <si>
     <t>登録済みの迷惑番号を、折り畳みのカードで一覧。絞り込み、新規登録、編集、削除</t>
@@ -209,7 +200,7 @@
     <t>/register</t>
   </si>
   <si>
-    <t>電話先（任意）、伝言内容、自分の名前、伝言先を入力</t>
+    <t>電話番号（任意。入力すると、迷惑番号か自動で確認）、電話先（任意）、伝言内容、自分の名前、伝言先を入力</t>
   </si>
   <si>
     <t>確認</t>
@@ -248,19 +239,25 @@
     <t>1件の全文。受電者、電話先、日時</t>
   </si>
   <si>
-    <t>4.1 迷惑電話チェック（/nuisance）</t>
-  </si>
-  <si>
-    <t>・入力: 電話番号。全角、ハイフンの有無、+81 付きでも同じ番号として扱う。</t>
-  </si>
-  <si>
-    <t>・桁数: 8〜15桁の数字。足りないとき「電話番号を入力してください」。</t>
-  </si>
-  <si>
-    <t>・結果「登録なし」: 緑の札。「伝言を登録する」（登録フォームへ。本文に TEL：番号 が入る）、「迷惑番号として登録する」（迷惑番号一覧の登録フォームへ。番号が入る）。</t>
-  </si>
-  <si>
-    <t>・結果「登録されています」: 赤い札と、迷惑番号のカード（最初から開いた状態）。「今回の着信を記録する」（対応者・メモ）で着信ログを追加できる。</t>
+    <t>4.1 登録フォームの、迷惑番号の自動チェック（/register）</t>
+  </si>
+  <si>
+    <t>・入力: 電話番号（任意）。全角、ハイフンの有無、+81 付きでも同じ番号として扱う。画面を開いたとき、この欄にカーソルがある。</t>
+  </si>
+  <si>
+    <t>・確認のタイミング: 8桁以上になって、入力が0.5秒止まったとき。入力のたびには確認しない。確認中は「迷惑番号か確認しています…」。</t>
+  </si>
+  <si>
+    <t>・結果「登録されています」: 赤い札と、迷惑番号のカード（閉じた状態。電話番号と会社名だけ）。カードを開くと、メモ・着信ログの確認と、「今回の着信を記録する」（対応者・メモ）ができる。登録されていても、伝言の登録は続けられる。</t>
+  </si>
+  <si>
+    <t>・結果「登録なし」: 緑の「✓ 〇〇 は、迷惑番号には登録されていません」と、「迷惑番号として登録する」（迷惑番号一覧の登録フォームへ。番号が入る）。</t>
+  </si>
+  <si>
+    <t>・確認に失敗したとき: エラーの文言（登録フォームの入力は続けられる）。</t>
+  </si>
+  <si>
+    <t>・入力した電話番号は、伝言の本文の最後に「TEL：番号」の1行として加える（本文に同じ番号がすでにあれば、加えない）。確認画面で、「修正する」を押しても、電話番号は残る。</t>
   </si>
   <si>
     <t>4.2 迷惑番号のカード（検索結果と一覧で共通）</t>
@@ -294,6 +291,9 @@
   </si>
   <si>
     <t>4.4 登録フォーム → 確認 → 完了</t>
+  </si>
+  <si>
+    <t>・電話番号の自動チェックは、4.1。</t>
   </si>
   <si>
     <t>・必須: 伝言内容、自分の名前（受電者）、伝言先。未入力のとき、「伝言内容を入力してください」「自分の名前を入力してください」「伝言先を選択してください」。</t>
@@ -1118,7 +1118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1567,11 +1567,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1582,7 +1582,7 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="3" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>48</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>60</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>63</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>66</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>69</v>
       </c>
@@ -1677,213 +1677,226 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
     </row>
-    <row r="19" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+    <row r="20" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
+    <row r="24" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
     </row>
-    <row r="28" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+    <row r="32" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-    </row>
-    <row r="34" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-    </row>
-    <row r="35" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
     </row>
-    <row r="36" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
     </row>
-    <row r="37" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+    <row r="38" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+    </row>
+    <row r="39" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-    </row>
-    <row r="40" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+    </row>
+    <row r="42" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-    </row>
-    <row r="41" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-    </row>
-    <row r="42" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
     </row>
+    <row r="43" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="29">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A44:C44"/>
   </mergeCells>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/docs/excel/仕様書.xlsx
+++ b/docs/excel/仕様書.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="210">
   <si>
     <t>伝言メモ 仕様書</t>
   </si>
@@ -35,7 +35,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.2（リリース前の下書き。迷惑番号の確認を、登録フォームに統合）</t>
+    <t>0.3（リリース前の下書き。登録フォームから、直接の登録もできる）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -95,10 +95,13 @@
     <t xml:space="preserve">       └ 登録なし</t>
   </si>
   <si>
-    <t xml:space="preserve">            ├ 通常の電話 → そのまま伝言を入力 → 確認 → 登録 → Teams に通知</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            └ 迷惑電話だった → 「迷惑番号として登録する」→ 迷惑番号一覧の登録フォーム</t>
+    <t xml:space="preserve">            ├ 通常の電話 → 伝言を入力 →「このまま伝言を登録する」（確認画面なし）→ 伝言一覧へ → Teams に通知</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            │             （確認してから登録したいときは、「確認」→「最終OK」）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            └ 迷惑電話だった → 「迷惑番号として登録する」→ その場で、会社名・メモを入れて登録（着信も1件、記録）</t>
   </si>
   <si>
     <t>画面上部の矢印のタブは、この順（登録フォーム → 伝言一覧 → 迷惑番号一覧）に並ぶ。</t>
@@ -251,7 +254,13 @@
     <t>・結果「登録されています」: 赤い札と、迷惑番号のカード（閉じた状態。電話番号と会社名だけ）。カードを開くと、メモ・着信ログの確認と、「今回の着信を記録する」（対応者・メモ）ができる。登録されていても、伝言の登録は続けられる。</t>
   </si>
   <si>
-    <t>・結果「登録なし」: 緑の「✓ 〇〇 は、迷惑番号には登録されていません」と、「迷惑番号として登録する」（迷惑番号一覧の登録フォームへ。番号が入る）。</t>
+    <t>・結果「登録なし」: 緑の「✓ 〇〇 は、迷惑番号には登録されていません」と、次の2つのボタン。どちらも、画面を移らずに、その場で行う。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ・「このまま伝言を登録する」: 確認画面と完了画面を飛ばして、伝言を登録し、伝言一覧へ移る。必須の項目（伝言内容・自分の名前・伝言先）が空のときは、ボタンの下に、足りない項目を知らせて、登録しない。登録に失敗したときは、「伝言を登録できませんでした。もう一度お試しください」と出て、入力は残る。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ・「迷惑番号として登録する」: 会社名（登録フォームの電話先が入る）とメモの小さなフォームが開く。「登録する」で、迷惑番号に登録し、着信も1件、記録する（対応者は、自分の名前）。登録後は、その番号が、赤い札とカードで出る。</t>
   </si>
   <si>
     <t>・確認に失敗したとき: エラーの文言（登録フォームの入力は続けられる）。</t>
@@ -293,7 +302,7 @@
     <t>4.4 登録フォーム → 確認 → 完了</t>
   </si>
   <si>
-    <t>・電話番号の自動チェックは、4.1。</t>
+    <t>・電話番号の自動チェックと、確認を通らない直接の登録は、4.1。確認を通る登録（「確認」→「最終OK」）も、そのまま使える。</t>
   </si>
   <si>
     <t>・必須: 伝言内容、自分の名前（受電者）、伝言先。未入力のとき、「伝言内容を入力してください」「自分の名前を入力してください」「伝言先を選択してください」。</t>
@@ -309,6 +318,9 @@
   </si>
   <si>
     <t>4.5 伝言一覧・詳細</t>
+  </si>
+  <si>
+    <t>・「このまま伝言を登録する」で登録した直後は、一覧の上に、「〇〇 宛の伝言を登録しました。」と、通知についての文言（本番「Teamsへ通知しました。」／テスト「テスト用チャネル（99_テスト）へ通知しました。」／仮データ「テストモードのため、Teamsには通知していません。」）が出る。登録した伝言が、いちばん上に出る。</t>
   </si>
   <si>
     <t>・一覧: 1件の枠の高さは一定。電話先は1行、内容は2行までで、あふれた分は「…」。電話先がないときは「（電話先なし）」。枠（電話先・内容の部分、または宛先）をクリックすると詳細へ。</t>
@@ -1181,14 +1193,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1196,66 +1208,66 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -1281,14 +1293,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1296,42 +1308,42 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -1398,7 +1410,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1439,9 +1451,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1465,7 +1482,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1473,63 +1490,63 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1537,7 +1554,7 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1545,7 +1562,7 @@
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1567,7 +1584,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1577,24 +1594,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>2</v>
@@ -1602,272 +1619,293 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
     </row>
-    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-    </row>
-    <row r="24" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+    <row r="33" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-    </row>
-    <row r="36" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
     </row>
-    <row r="38" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
     </row>
-    <row r="39" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-    </row>
-    <row r="42" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+    <row r="40" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-    </row>
-    <row r="43" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-    </row>
-    <row r="44" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+    </row>
+    <row r="44" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
     </row>
+    <row r="45" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+    </row>
+    <row r="47" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="32">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A14:C14"/>
@@ -1877,26 +1915,29 @@
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
   </mergeCells>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1917,7 +1958,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1925,7 +1966,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1933,7 +1974,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1941,7 +1982,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1949,91 +1990,91 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2041,7 +2082,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2049,105 +2090,105 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2155,7 +2196,7 @@
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2190,17 +2231,17 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
@@ -2208,47 +2249,47 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2276,32 +2317,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2322,27 +2363,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/仕様書.xlsx
+++ b/docs/excel/仕様書.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="225">
   <si>
     <t>伝言メモ 仕様書</t>
   </si>
@@ -35,7 +35,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.3（リリース前の下書き。登録フォームから、直接の登録もできる）</t>
+    <t>0.4（リリース前の下書き。ボタンの色の使い分けを追加）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -330,6 +330,51 @@
   </si>
   <si>
     <t>・詳細: 伝言先、日時、電話先、伝言内容（改行をそのまま）、受電者。</t>
+  </si>
+  <si>
+    <t>4.6 ボタンの色の使い分け</t>
+  </si>
+  <si>
+    <t>色</t>
+  </si>
+  <si>
+    <t>使う操作</t>
+  </si>
+  <si>
+    <t>緑（会社の色）</t>
+  </si>
+  <si>
+    <t>伝言を登録する（「このまま伝言を登録する」「確認して登録する」「最終OK」）、そのほかの主な操作</t>
+  </si>
+  <si>
+    <t>黄（アンバー）</t>
+  </si>
+  <si>
+    <t>迷惑番号に関する操作（「迷惑番号として登録する」、迷惑番号の登録・更新、「今回の着信を記録する」、迷惑番号一覧の「新規登録」）</t>
+  </si>
+  <si>
+    <t>赤</t>
+  </si>
+  <si>
+    <t>削除（ゴミ箱）。登録済みの迷惑番号の札</t>
+  </si>
+  <si>
+    <t>白地に緑の枠</t>
+  </si>
+  <si>
+    <t>取り消し・戻るなどの、副次的な操作（「やめる」「キャンセル」）</t>
+  </si>
+  <si>
+    <t>・登録なしの結果では、2つのボタンの上に、「ふつうの電話のとき」「迷惑電話だったとき」と、使う場面を添える。幅の狭い画面では、縦に並べる。</t>
+  </si>
+  <si>
+    <t>・通信中は、ボタンの中と、確認中の文言の横に、くるくる回る印を出す。ボタンは、通信中は押せない。</t>
+  </si>
+  <si>
+    <t>・登録直後の、伝言一覧のお知らせは、アイコン付きで、閉じるボタン（×）がある。</t>
+  </si>
+  <si>
+    <t>・黄のボタンの文字は、濃い茶色（コントラスト比 8:1 以上）。</t>
   </si>
   <si>
     <t>5. API</t>
@@ -1130,7 +1175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1193,14 +1238,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1208,66 +1253,66 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -1293,14 +1338,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1308,42 +1353,42 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -1584,12 +1629,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="2" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1701,14 +1745,14 @@
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
-    <row r="15" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
     </row>
-    <row r="16" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>75</v>
       </c>
@@ -1904,8 +1948,83 @@
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
     </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+    </row>
+    <row r="50" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+    </row>
+    <row r="57" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+    </row>
+    <row r="58" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+    </row>
+    <row r="59" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="37">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A14:C14"/>
@@ -1938,6 +2057,11 @@
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A59:C59"/>
   </mergeCells>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1958,7 +2082,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1966,7 +2090,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1974,7 +2098,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1982,7 +2106,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1990,91 +2114,91 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2082,7 +2206,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2090,105 +2214,105 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2196,7 +2320,7 @@
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2231,17 +2355,17 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
@@ -2249,47 +2373,47 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2317,32 +2441,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2363,27 +2487,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/仕様書.xlsx
+++ b/docs/excel/仕様書.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="226">
   <si>
     <t>伝言メモ 仕様書</t>
   </si>
@@ -35,7 +35,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.4（リリース前の下書き。ボタンの色の使い分けを追加）</t>
+    <t>0.5（リリース前の下書き。緑のボタンを1つにまとめた）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">       └ 登録なし</t>
   </si>
   <si>
-    <t xml:space="preserve">            ├ 通常の電話 → 伝言を入力 →「このまま伝言を登録する」（確認画面なし）→ 伝言一覧へ → Teams に通知</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            │             （確認してから登録したいときは、「確認」→「最終OK」）</t>
+    <t xml:space="preserve">            ├ 通常の電話 → 伝言を入力 → フォーム下の「登録する」（確認画面なし）→ 伝言一覧へ → Teams に通知</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            │             （確認してから登録したいときは、「確認してから登録する」→「最終OK」）</t>
   </si>
   <si>
     <t xml:space="preserve">            └ 迷惑電話だった → 「迷惑番号として登録する」→ その場で、会社名・メモを入れて登録（着信も1件、記録）</t>
@@ -254,13 +254,16 @@
     <t>・結果「登録されています」: 赤い札と、迷惑番号のカード（閉じた状態。電話番号と会社名だけ）。カードを開くと、メモ・着信ログの確認と、「今回の着信を記録する」（対応者・メモ）ができる。登録されていても、伝言の登録は続けられる。</t>
   </si>
   <si>
-    <t>・結果「登録なし」: 緑の「✓ 〇〇 は、迷惑番号には登録されていません」と、次の2つのボタン。どちらも、画面を移らずに、その場で行う。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ・「このまま伝言を登録する」: 確認画面と完了画面を飛ばして、伝言を登録し、伝言一覧へ移る。必須の項目（伝言内容・自分の名前・伝言先）が空のときは、ボタンの下に、足りない項目を知らせて、登録しない。登録に失敗したときは、「伝言を登録できませんでした。もう一度お試しください」と出て、入力は残る。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ・「迷惑番号として登録する」: 会社名（登録フォームの電話先が入る）とメモの小さなフォームが開く。「登録する」で、迷惑番号に登録し、着信も1件、記録する（対応者は、自分の名前）。登録後は、その番号が、赤い札とカードで出る。</t>
+    <t>・結果「登録なし」: 緑の「✓ 〇〇 は、迷惑番号には登録されていません」と、黄のボタン「迷惑番号として登録する」（上に「迷惑電話だったとき」と添える）。押すと、画面を移らずに、会社名（登録フォームの電話先が入る）とメモの小さなフォームが開き、「迷惑番号に登録する」で、迷惑番号に登録し、着信も1件、記録する（対応者は、自分の名前）。登録後は、その番号が、赤い札とカードで出る。</t>
+  </si>
+  <si>
+    <t>・フォーム下のボタン（電話番号の確認の結果に関わらず、いつも出る）:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ・緑「登録する」: 確認画面と完了画面を飛ばして、伝言を登録し、伝言一覧へ移る。必須の項目（伝言内容・自分の名前・伝言先）が空のときは、ボタンの上に、足りない項目を知らせて、登録しない。登録に失敗したときは、「伝言を登録できませんでした。もう一度お試しください」と出て、入力は残る。登録中は、押せない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ・白地に緑の枠「確認してから登録する」: 確認画面（「修正する」「最終OK」）を通って登録する。</t>
   </si>
   <si>
     <t>・確認に失敗したとき: エラーの文言（登録フォームの入力は続けられる）。</t>
@@ -320,7 +323,7 @@
     <t>4.5 伝言一覧・詳細</t>
   </si>
   <si>
-    <t>・「このまま伝言を登録する」で登録した直後は、一覧の上に、「〇〇 宛の伝言を登録しました。」と、通知についての文言（本番「Teamsへ通知しました。」／テスト「テスト用チャネル（99_テスト）へ通知しました。」／仮データ「テストモードのため、Teamsには通知していません。」）が出る。登録した伝言が、いちばん上に出る。</t>
+    <t>・フォーム下の「登録する」で登録した直後は、一覧の上に、「〇〇 宛の伝言を登録しました。」と、通知についての文言（本番「Teamsへ通知しました。」／テスト「テスト用チャネル（99_テスト）へ通知しました。」／仮データ「テストモードのため、Teamsには通知していません。」）が出る。登録した伝言が、いちばん上に出る。</t>
   </si>
   <si>
     <t>・一覧: 1件の枠の高さは一定。電話先は1行、内容は2行までで、あふれた分は「…」。電話先がないときは「（電話先なし）」。枠（電話先・内容の部分、または宛先）をクリックすると詳細へ。</t>
@@ -344,7 +347,7 @@
     <t>緑（会社の色）</t>
   </si>
   <si>
-    <t>伝言を登録する（「このまま伝言を登録する」「確認して登録する」「最終OK」）、そのほかの主な操作</t>
+    <t>伝言を登録する（フォーム下の「登録する」、確認画面の「最終OK」）。1つの画面で、緑の主な操作は、1つだけ</t>
   </si>
   <si>
     <t>黄（アンバー）</t>
@@ -362,10 +365,10 @@
     <t>白地に緑の枠</t>
   </si>
   <si>
-    <t>取り消し・戻るなどの、副次的な操作（「やめる」「キャンセル」）</t>
-  </si>
-  <si>
-    <t>・登録なしの結果では、2つのボタンの上に、「ふつうの電話のとき」「迷惑電話だったとき」と、使う場面を添える。幅の狭い画面では、縦に並べる。</t>
+    <t>副次的な操作（「確認してから登録する」「やめる」「キャンセル」）</t>
+  </si>
+  <si>
+    <t>・黄のボタンの上に、「迷惑電話だったとき」と、使う場面を添える。フォーム下の2つのボタンは、幅の狭い画面では、縦に並べる（緑が上）。</t>
   </si>
   <si>
     <t>・通信中は、ボタンの中と、確認中の文言の横に、くるくる回る印を出す。ボタンは、通信中は押せない。</t>
@@ -1238,14 +1241,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1253,66 +1256,66 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -1338,14 +1341,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1353,42 +1356,42 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1632,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1766,21 +1769,21 @@
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
     </row>
-    <row r="18" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
     </row>
-    <row r="19" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
     </row>
-    <row r="20" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>79</v>
       </c>
@@ -1794,47 +1797,47 @@
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
     </row>
-    <row r="22" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+    <row r="23" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+    <row r="27" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -1871,28 +1874,28 @@
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+    <row r="35" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-    </row>
-    <row r="38" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
     </row>
-    <row r="39" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>95</v>
       </c>
@@ -1906,35 +1909,35 @@
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
     </row>
-    <row r="41" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+    <row r="42" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-    </row>
-    <row r="44" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-    </row>
-    <row r="45" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+    </row>
+    <row r="45" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
     </row>
-    <row r="46" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>101</v>
       </c>
@@ -1948,61 +1951,61 @@
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+    <row r="48" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-    </row>
-    <row r="50" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+    </row>
+    <row r="51" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="51" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="4" t="s">
+    </row>
+    <row r="52" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="52" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+      <c r="B52" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B52" s="4" t="s">
+    </row>
+    <row r="53" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="53" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="B53" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B53" s="4" t="s">
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="54" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="B54" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B54" s="4" t="s">
+    </row>
+    <row r="55" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="56" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-    </row>
-    <row r="57" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>115</v>
       </c>
@@ -2023,8 +2026,15 @@
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
     </row>
+    <row r="60" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="38">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A14:C14"/>
@@ -2036,32 +2046,33 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
   </mergeCells>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -2082,7 +2093,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2090,7 +2101,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2098,7 +2109,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2106,7 +2117,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2114,91 +2125,91 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2206,7 +2217,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2214,105 +2225,105 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2320,7 +2331,7 @@
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2355,17 +2366,17 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
@@ -2373,47 +2384,47 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2441,32 +2452,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2487,27 +2498,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/仕様書.xlsx
+++ b/docs/excel/仕様書.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="220">
   <si>
     <t>伝言メモ 仕様書</t>
   </si>
@@ -35,7 +35,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.5（リリース前の下書き。緑のボタンを1つにまとめた）</t>
+    <t>0.6（リリース前の下書き。確認画面・完了画面をなくし、枠のデザインを整理）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -95,10 +95,7 @@
     <t xml:space="preserve">       └ 登録なし</t>
   </si>
   <si>
-    <t xml:space="preserve">            ├ 通常の電話 → 伝言を入力 → フォーム下の「登録する」（確認画面なし）→ 伝言一覧へ → Teams に通知</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            │             （確認してから登録したいときは、「確認してから登録する」→「最終OK」）</t>
+    <t xml:space="preserve">            ├ 通常の電話 → 伝言を入力 → フォーム下の「登録する」（確認画面はない）→ 伝言一覧へ → Teams に通知</t>
   </si>
   <si>
     <t xml:space="preserve">            └ 迷惑電話だった → 「迷惑番号として登録する」→ その場で、会社名・メモを入れて登録（着信も1件、記録）</t>
@@ -170,7 +167,7 @@
     <t>4. 画面</t>
   </si>
   <si>
-    <t>共通: 上に矢印のタブ（登録の途中の「確認」「完了」では出さない）。スマホ幅（390px）で横にはみ出さない。</t>
+    <t>共通: 上に矢印のタブ。スマホ幅（390px）で横にはみ出さない。</t>
   </si>
   <si>
     <t>画面</t>
@@ -206,24 +203,6 @@
     <t>電話番号（任意。入力すると、迷惑番号か自動で確認）、電話先（任意）、伝言内容、自分の名前、伝言先を入力</t>
   </si>
   <si>
-    <t>確認</t>
-  </si>
-  <si>
-    <t>/confirm</t>
-  </si>
-  <si>
-    <t>入力内容を、電話先・伝言内容・受電者・伝言先に分けて表示。「修正する」「最終OK」</t>
-  </si>
-  <si>
-    <t>完了</t>
-  </si>
-  <si>
-    <t>/complete</t>
-  </si>
-  <si>
-    <t>登録した旨と、環境に応じた通知の文言</t>
-  </si>
-  <si>
     <t>伝言一覧</t>
   </si>
   <si>
@@ -260,16 +239,13 @@
     <t>・フォーム下のボタン（電話番号の確認の結果に関わらず、いつも出る）:</t>
   </si>
   <si>
-    <t xml:space="preserve">  ・緑「登録する」: 確認画面と完了画面を飛ばして、伝言を登録し、伝言一覧へ移る。必須の項目（伝言内容・自分の名前・伝言先）が空のときは、ボタンの上に、足りない項目を知らせて、登録しない。登録に失敗したときは、「伝言を登録できませんでした。もう一度お試しください」と出て、入力は残る。登録中は、押せない。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ・白地に緑の枠「確認してから登録する」: 確認画面（「修正する」「最終OK」）を通って登録する。</t>
+    <t xml:space="preserve">  ・緑「登録する」（真ん中に1つ）: 確認画面を通らずに、伝言を登録し、伝言一覧へ移る。必須の項目（伝言内容・自分の名前・伝言先）が空のときは、ボタンの上に、足りない項目を知らせて、登録しない。登録に失敗したときは、「伝言を登録できませんでした。もう一度お試しください」と出て、入力は残る。登録中は、押せない。</t>
   </si>
   <si>
     <t>・確認に失敗したとき: エラーの文言（登録フォームの入力は続けられる）。</t>
   </si>
   <si>
-    <t>・入力した電話番号は、伝言の本文の最後に「TEL：番号」の1行として加える（本文に同じ番号がすでにあれば、加えない）。確認画面で、「修正する」を押しても、電話番号は残る。</t>
+    <t>・入力した電話番号は、伝言の本文の最後に「TEL：番号」の1行として加える（本文に同じ番号がすでにあれば、加えない）。</t>
   </si>
   <si>
     <t>4.2 迷惑番号のカード（検索結果と一覧で共通）</t>
@@ -302,10 +278,10 @@
     <t>・取得に失敗したとき: 「一覧の取得に失敗しました。もう一度お試しください」。</t>
   </si>
   <si>
-    <t>4.4 登録フォーム → 確認 → 完了</t>
-  </si>
-  <si>
-    <t>・電話番号の自動チェックと、確認を通らない直接の登録は、4.1。確認を通る登録（「確認」→「最終OK」）も、そのまま使える。</t>
+    <t>4.4 伝言の登録</t>
+  </si>
+  <si>
+    <t>・流れ: 登録フォーム →「登録する」→ 伝言一覧（確認画面・完了画面はない）。電話番号の自動チェックは、4.1。</t>
   </si>
   <si>
     <t>・必須: 伝言内容、自分の名前（受電者）、伝言先。未入力のとき、「伝言内容を入力してください」「自分の名前を入力してください」「伝言先を選択してください」。</t>
@@ -317,13 +293,10 @@
     <t>・自分の名前は、そのブラウザに覚える（次回から選択済み）。</t>
   </si>
   <si>
-    <t>・完了画面の文言: 本番「Teamsへ通知しました。」＋Teams チャネルへのリンク／テスト「テスト用チャネル（99_テスト）へ通知しました。」／仮データ「テストモードのため、Teamsには通知していません。」</t>
-  </si>
-  <si>
     <t>4.5 伝言一覧・詳細</t>
   </si>
   <si>
-    <t>・フォーム下の「登録する」で登録した直後は、一覧の上に、「〇〇 宛の伝言を登録しました。」と、通知についての文言（本番「Teamsへ通知しました。」／テスト「テスト用チャネル（99_テスト）へ通知しました。」／仮データ「テストモードのため、Teamsには通知していません。」）が出る。登録した伝言が、いちばん上に出る。</t>
+    <t>・フォーム下の「登録する」で登録した直後は、一覧の上に、「〇〇 宛の伝言を登録しました。」と、通知についての文言（本番「Teamsへ通知しました。」と、Teams チャネルへのリンク「Teamsで確認する →」／テスト「テスト用チャネル（99_テスト）へ通知しました。」／仮データ「テストモードのため、Teamsには通知していません。」）が出る。登録した伝言が、いちばん上に出る。</t>
   </si>
   <si>
     <t>・一覧: 1件の枠の高さは一定。電話先は1行、内容は2行までで、あふれた分は「…」。電話先がないときは「（電話先なし）」。枠（電話先・内容の部分、または宛先）をクリックすると詳細へ。</t>
@@ -347,7 +320,7 @@
     <t>緑（会社の色）</t>
   </si>
   <si>
-    <t>伝言を登録する（フォーム下の「登録する」、確認画面の「最終OK」）。1つの画面で、緑の主な操作は、1つだけ</t>
+    <t>伝言を登録する（フォーム下の「登録する」）。1つの画面で、緑の主な操作は、1つだけ</t>
   </si>
   <si>
     <t>黄（アンバー）</t>
@@ -365,7 +338,7 @@
     <t>白地に緑の枠</t>
   </si>
   <si>
-    <t>副次的な操作（「確認してから登録する」「やめる」「キャンセル」）</t>
+    <t>副次的な操作（「やめる」「キャンセル」）</t>
   </si>
   <si>
     <t>・黄のボタンの上に、「迷惑電話だったとき」と、使う場面を添える。フォーム下の2つのボタンは、幅の狭い画面では、縦に並べる（緑が上）。</t>
@@ -378,6 +351,15 @@
   </si>
   <si>
     <t>・黄のボタンの文字は、濃い茶色（コントラスト比 8:1 以上）。</t>
+  </si>
+  <si>
+    <t>4.7 枠のデザイン</t>
+  </si>
+  <si>
+    <t>・伝言のメモ、迷惑番号のカード、電話番号の確認の枠は、薄い緑の斜めの縞の枠の中に、白い面を置く、すっきりした額縁風の見た目で、そろえる（上に、細いテープ風の印）。</t>
+  </si>
+  <si>
+    <t>・色は、会社の緑の系統だけ。迷惑番号の小さなフォームだけ、黄の薄い色合い。</t>
   </si>
   <si>
     <t>5. API</t>
@@ -1178,7 +1160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1241,14 +1223,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1256,66 +1238,66 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -1341,14 +1323,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1356,42 +1338,42 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1440,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1499,14 +1481,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="10" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1530,7 +1507,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1538,63 +1515,63 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1602,7 +1579,7 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1610,7 +1587,7 @@
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1641,24 +1618,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>2</v>
@@ -1666,377 +1643,364 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="4" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
     </row>
-    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
     </row>
-    <row r="17" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
     </row>
-    <row r="20" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
     </row>
-    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+    <row r="28" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
     </row>
-    <row r="33" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
+    <row r="36" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
     </row>
-    <row r="39" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-    </row>
-    <row r="40" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-    </row>
-    <row r="41" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+    </row>
+    <row r="41" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
     </row>
     <row r="42" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+    <row r="43" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+    </row>
+    <row r="47" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-    </row>
-    <row r="45" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+    </row>
+    <row r="49" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-    </row>
-    <row r="46" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="B49" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-    </row>
-    <row r="47" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-    </row>
-    <row r="48" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-    </row>
-    <row r="51" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="B51" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B51" s="2" t="s">
+    </row>
+    <row r="53" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="52" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+    </row>
+    <row r="55" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="53" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+    </row>
+    <row r="56" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="54" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+    </row>
+    <row r="59" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="55" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-    </row>
-    <row r="58" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-    </row>
-    <row r="59" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
     </row>
     <row r="60" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
@@ -2044,32 +2008,31 @@
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="A60:C60"/>
@@ -2093,7 +2056,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2101,7 +2064,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2109,7 +2072,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2117,7 +2080,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2125,91 +2088,91 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2217,7 +2180,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2225,105 +2188,105 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2331,7 +2294,7 @@
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2366,17 +2329,17 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
@@ -2384,47 +2347,47 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2452,32 +2415,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2498,27 +2461,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
